--- a/data/nzd0090/nzd0090.xlsx
+++ b/data/nzd0090/nzd0090.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M315"/>
+  <dimension ref="A1:M316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14623,6 +14623,51 @@
       <c r="M315" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>308.96</v>
+      </c>
+      <c r="C316" t="n">
+        <v>301.05</v>
+      </c>
+      <c r="D316" t="n">
+        <v>296.01</v>
+      </c>
+      <c r="E316" t="n">
+        <v>296.38</v>
+      </c>
+      <c r="F316" t="n">
+        <v>303.25</v>
+      </c>
+      <c r="G316" t="n">
+        <v>312.49</v>
+      </c>
+      <c r="H316" t="n">
+        <v>315.51</v>
+      </c>
+      <c r="I316" t="n">
+        <v>325.04</v>
+      </c>
+      <c r="J316" t="n">
+        <v>333.83</v>
+      </c>
+      <c r="K316" t="n">
+        <v>339.7</v>
+      </c>
+      <c r="L316" t="n">
+        <v>327.91</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -14637,7 +14682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B323"/>
+  <dimension ref="A1:B324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17870,6 +17915,16 @@
       </c>
       <c r="B323" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -18038,28 +18093,28 @@
         <v>0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1410983169608582</v>
+        <v>0.138986243816358</v>
       </c>
       <c r="J2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K2" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05746803395558797</v>
+        <v>0.05612404088931366</v>
       </c>
       <c r="M2" t="n">
-        <v>3.015883210743791</v>
+        <v>3.017424329856534</v>
       </c>
       <c r="N2" t="n">
-        <v>17.48178177640092</v>
+        <v>17.46029607724985</v>
       </c>
       <c r="O2" t="n">
-        <v>4.181122071454135</v>
+        <v>4.178551911517894</v>
       </c>
       <c r="P2" t="n">
-        <v>308.4705485283084</v>
+        <v>308.4936791024159</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18116,28 +18171,28 @@
         <v>0.1027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1382257309433595</v>
+        <v>0.1369589940209135</v>
       </c>
       <c r="J3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K3" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05560755316534094</v>
+        <v>0.05497578416778015</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08021760678041</v>
+        <v>3.076549040623528</v>
       </c>
       <c r="N3" t="n">
-        <v>17.37275874994229</v>
+        <v>17.32984166755044</v>
       </c>
       <c r="O3" t="n">
-        <v>4.168064148971593</v>
+        <v>4.162912642315527</v>
       </c>
       <c r="P3" t="n">
-        <v>299.3278133296033</v>
+        <v>299.3416861219996</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18194,28 +18249,28 @@
         <v>0.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08114908267141102</v>
+        <v>0.0789820977293665</v>
       </c>
       <c r="J4" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K4" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0143644035683359</v>
+        <v>0.01369241249871267</v>
       </c>
       <c r="M4" t="n">
-        <v>3.611141956359163</v>
+        <v>3.609371161482966</v>
       </c>
       <c r="N4" t="n">
-        <v>24.19180596111264</v>
+        <v>24.15081014555653</v>
       </c>
       <c r="O4" t="n">
-        <v>4.918516642353937</v>
+        <v>4.914347377379475</v>
       </c>
       <c r="P4" t="n">
-        <v>297.2163528345711</v>
+        <v>297.2400847805609</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18272,28 +18327,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09806393408261989</v>
+        <v>0.09482764239991054</v>
       </c>
       <c r="J5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K5" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02083086488590524</v>
+        <v>0.01957627563587427</v>
       </c>
       <c r="M5" t="n">
-        <v>3.786036061551657</v>
+        <v>3.787044595693895</v>
       </c>
       <c r="N5" t="n">
-        <v>24.20144608702167</v>
+        <v>24.20447252023417</v>
       </c>
       <c r="O5" t="n">
-        <v>4.919496527798517</v>
+        <v>4.919804114010452</v>
       </c>
       <c r="P5" t="n">
-        <v>298.7978323038481</v>
+        <v>298.8332748664296</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18350,28 +18405,28 @@
         <v>0.0916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07618693699402361</v>
+        <v>0.07351775140697561</v>
       </c>
       <c r="J6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K6" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01343591956713619</v>
+        <v>0.01258004163795823</v>
       </c>
       <c r="M6" t="n">
-        <v>3.826388734250254</v>
+        <v>3.826347822172364</v>
       </c>
       <c r="N6" t="n">
-        <v>22.81871637949495</v>
+        <v>22.80059754946264</v>
       </c>
       <c r="O6" t="n">
-        <v>4.776894009656792</v>
+        <v>4.774997125597316</v>
       </c>
       <c r="P6" t="n">
-        <v>305.3642909358269</v>
+        <v>305.3935227809403</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18428,28 +18483,28 @@
         <v>0.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08183977885549482</v>
+        <v>0.07882184790501397</v>
       </c>
       <c r="J7" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K7" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01890002254868806</v>
+        <v>0.01761263932054968</v>
       </c>
       <c r="M7" t="n">
-        <v>3.388401430562493</v>
+        <v>3.392363567965353</v>
       </c>
       <c r="N7" t="n">
-        <v>18.61453179149197</v>
+        <v>18.62488178335287</v>
       </c>
       <c r="O7" t="n">
-        <v>4.31445614087013</v>
+        <v>4.315655429173288</v>
       </c>
       <c r="P7" t="n">
-        <v>314.9990822108873</v>
+        <v>315.0321333747087</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18506,28 +18561,28 @@
         <v>0.0945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06822041358996381</v>
+        <v>0.06568720372633052</v>
       </c>
       <c r="J8" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K8" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0128326102384928</v>
+        <v>0.01196109723686845</v>
       </c>
       <c r="M8" t="n">
-        <v>3.398934602303586</v>
+        <v>3.401933485613759</v>
       </c>
       <c r="N8" t="n">
-        <v>19.16799872548869</v>
+        <v>19.15607586871769</v>
       </c>
       <c r="O8" t="n">
-        <v>4.378127308049492</v>
+        <v>4.376765457357486</v>
       </c>
       <c r="P8" t="n">
-        <v>317.6314243576905</v>
+        <v>317.6591670514667</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18584,28 +18639,28 @@
         <v>0.0588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1666827665861998</v>
+        <v>0.1651079317833358</v>
       </c>
       <c r="J9" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K9" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05961405756574689</v>
+        <v>0.05890218827698046</v>
       </c>
       <c r="M9" t="n">
-        <v>3.516464349772363</v>
+        <v>3.511496128558194</v>
       </c>
       <c r="N9" t="n">
-        <v>23.46449032986467</v>
+        <v>23.40890957982873</v>
       </c>
       <c r="O9" t="n">
-        <v>4.844015929976353</v>
+        <v>4.838275475810439</v>
       </c>
       <c r="P9" t="n">
-        <v>323.03178649338</v>
+        <v>323.0490334496275</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18662,28 +18717,28 @@
         <v>0.0578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.05311700771467393</v>
+        <v>0.04986387778425048</v>
       </c>
       <c r="J10" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K10" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006268308247480259</v>
+        <v>0.00554823575061314</v>
       </c>
       <c r="M10" t="n">
-        <v>3.401008973950082</v>
+        <v>3.402577424421729</v>
       </c>
       <c r="N10" t="n">
-        <v>23.94739500136792</v>
+        <v>23.95206108486239</v>
       </c>
       <c r="O10" t="n">
-        <v>4.893607565116754</v>
+        <v>4.894084294825988</v>
       </c>
       <c r="P10" t="n">
-        <v>337.4713614132225</v>
+        <v>337.5069883815087</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18740,28 +18795,28 @@
         <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01237984260141112</v>
+        <v>0.01196935367216915</v>
       </c>
       <c r="J11" t="n">
+        <v>315</v>
+      </c>
+      <c r="K11" t="n">
         <v>314</v>
       </c>
-      <c r="K11" t="n">
-        <v>313</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.0005009179061092883</v>
+        <v>0.0004715372010777319</v>
       </c>
       <c r="M11" t="n">
-        <v>2.969499763026572</v>
+        <v>2.962296079686862</v>
       </c>
       <c r="N11" t="n">
-        <v>16.41171589499996</v>
+        <v>16.36073332254018</v>
       </c>
       <c r="O11" t="n">
-        <v>4.051137605043793</v>
+        <v>4.044840333380315</v>
       </c>
       <c r="P11" t="n">
-        <v>340.0025936406203</v>
+        <v>340.0070816932176</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18818,28 +18873,28 @@
         <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07848593747329485</v>
+        <v>0.07610007751315462</v>
       </c>
       <c r="J12" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K12" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01292519838439943</v>
+        <v>0.0122245357714692</v>
       </c>
       <c r="M12" t="n">
-        <v>3.928234918377953</v>
+        <v>3.926258177364057</v>
       </c>
       <c r="N12" t="n">
-        <v>25.18655835360472</v>
+        <v>25.15000249402123</v>
       </c>
       <c r="O12" t="n">
-        <v>5.018621160598269</v>
+        <v>5.014977815905193</v>
       </c>
       <c r="P12" t="n">
-        <v>329.5271412327938</v>
+        <v>329.5532702097954</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18877,7 +18932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M315"/>
+  <dimension ref="A1:M316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39981,6 +40036,73 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:11:19+00:00</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>-35.55974867849579,174.4861468097969</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>-35.560108118679835,174.48693492347604</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>-35.5604437756514,174.4877355030819</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-35.560734601390735,174.4885595802285</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-35.560972279194004,174.48941393805487</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-35.56119377880986,174.49030620216791</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-35.561394627322954,174.49119926653032</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-35.56153204929617,174.49208671391537</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-35.5616832089509,174.49300781583977</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-35.56168422920465,174.49394573363458</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-35.561805334612984,174.49484853507252</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0090/nzd0090.xlsx
+++ b/data/nzd0090/nzd0090.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M316"/>
+  <dimension ref="A1:M318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14666,6 +14666,96 @@
         <v>327.91</v>
       </c>
       <c r="M316" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="n">
+        <v>307.93</v>
+      </c>
+      <c r="C317" t="n">
+        <v>300.19</v>
+      </c>
+      <c r="D317" t="n">
+        <v>296.17</v>
+      </c>
+      <c r="E317" t="n">
+        <v>296.88</v>
+      </c>
+      <c r="F317" t="n">
+        <v>302.55</v>
+      </c>
+      <c r="G317" t="n">
+        <v>312.36</v>
+      </c>
+      <c r="H317" t="n">
+        <v>314.19</v>
+      </c>
+      <c r="I317" t="n">
+        <v>322.98</v>
+      </c>
+      <c r="J317" t="n">
+        <v>331.42</v>
+      </c>
+      <c r="K317" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="L317" t="n">
+        <v>328.34</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>310.17</v>
+      </c>
+      <c r="C318" t="n">
+        <v>302</v>
+      </c>
+      <c r="D318" t="n">
+        <v>296.91</v>
+      </c>
+      <c r="E318" t="n">
+        <v>297.9</v>
+      </c>
+      <c r="F318" t="n">
+        <v>303.18</v>
+      </c>
+      <c r="G318" t="n">
+        <v>313.22</v>
+      </c>
+      <c r="H318" t="n">
+        <v>315.83</v>
+      </c>
+      <c r="I318" t="n">
+        <v>325.25</v>
+      </c>
+      <c r="J318" t="n">
+        <v>333.33</v>
+      </c>
+      <c r="K318" t="n">
+        <v>340.83</v>
+      </c>
+      <c r="L318" t="n">
+        <v>330.37</v>
+      </c>
+      <c r="M318" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14682,7 +14772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B324"/>
+  <dimension ref="A1:B326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17925,6 +18015,26 @@
       </c>
       <c r="B324" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0.48</v>
       </c>
     </row>
   </sheetData>
@@ -18093,28 +18203,28 @@
         <v>0.0819</v>
       </c>
       <c r="I2" t="n">
-        <v>0.138986243816358</v>
+        <v>0.1349662332214596</v>
       </c>
       <c r="J2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K2" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05612404088931366</v>
+        <v>0.05359549837937616</v>
       </c>
       <c r="M2" t="n">
-        <v>3.017424329856534</v>
+        <v>3.019742042105481</v>
       </c>
       <c r="N2" t="n">
-        <v>17.46029607724985</v>
+        <v>17.42035521681591</v>
       </c>
       <c r="O2" t="n">
-        <v>4.178551911517894</v>
+        <v>4.173769904632491</v>
       </c>
       <c r="P2" t="n">
-        <v>308.4936791024159</v>
+        <v>308.5378367431006</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -18171,28 +18281,28 @@
         <v>0.1027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1369589940209135</v>
+        <v>0.1345227084826111</v>
       </c>
       <c r="J3" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K3" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05497578416778015</v>
+        <v>0.05376453447571394</v>
       </c>
       <c r="M3" t="n">
-        <v>3.076549040623528</v>
+        <v>3.068743104486169</v>
       </c>
       <c r="N3" t="n">
-        <v>17.32984166755044</v>
+        <v>17.24855848853416</v>
       </c>
       <c r="O3" t="n">
-        <v>4.162912642315527</v>
+        <v>4.153138390245883</v>
       </c>
       <c r="P3" t="n">
-        <v>299.3416861219996</v>
+        <v>299.3684459661976</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -18249,28 +18359,28 @@
         <v>0.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0789820977293665</v>
+        <v>0.07540597735995572</v>
       </c>
       <c r="J4" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K4" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01369241249871267</v>
+        <v>0.01264313715603049</v>
       </c>
       <c r="M4" t="n">
-        <v>3.609371161482966</v>
+        <v>3.602502232705304</v>
       </c>
       <c r="N4" t="n">
-        <v>24.15081014555653</v>
+        <v>24.04856212054601</v>
       </c>
       <c r="O4" t="n">
-        <v>4.914347377379475</v>
+        <v>4.9039333315764</v>
       </c>
       <c r="P4" t="n">
-        <v>297.2400847805609</v>
+        <v>297.279370520709</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -18327,28 +18437,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09482764239991054</v>
+        <v>0.08977442764723026</v>
       </c>
       <c r="J5" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K5" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01957627563587427</v>
+        <v>0.01775153850557531</v>
       </c>
       <c r="M5" t="n">
-        <v>3.787044595693895</v>
+        <v>3.783253503192385</v>
       </c>
       <c r="N5" t="n">
-        <v>24.20447252023417</v>
+        <v>24.15176735008963</v>
       </c>
       <c r="O5" t="n">
-        <v>4.919804114010452</v>
+        <v>4.914444765188599</v>
       </c>
       <c r="P5" t="n">
-        <v>298.8332748664296</v>
+        <v>298.8887874117859</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -18405,28 +18515,28 @@
         <v>0.0916</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07351775140697561</v>
+        <v>0.06781759593172065</v>
       </c>
       <c r="J6" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K6" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01258004163795823</v>
+        <v>0.0108148164183145</v>
       </c>
       <c r="M6" t="n">
-        <v>3.826347822172364</v>
+        <v>3.827727754131471</v>
       </c>
       <c r="N6" t="n">
-        <v>22.80059754946264</v>
+        <v>22.78250634910999</v>
       </c>
       <c r="O6" t="n">
-        <v>4.774997125597316</v>
+        <v>4.773102382005857</v>
       </c>
       <c r="P6" t="n">
-        <v>305.3935227809403</v>
+        <v>305.4561440223089</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -18483,28 +18593,28 @@
         <v>0.1115</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07882184790501397</v>
+        <v>0.07330272958501111</v>
       </c>
       <c r="J7" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K7" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01761263932054968</v>
+        <v>0.015383305375545</v>
       </c>
       <c r="M7" t="n">
-        <v>3.392363567965353</v>
+        <v>3.39798849834539</v>
       </c>
       <c r="N7" t="n">
-        <v>18.62488178335287</v>
+        <v>18.6258497651653</v>
       </c>
       <c r="O7" t="n">
-        <v>4.315655429173288</v>
+        <v>4.315767575433749</v>
       </c>
       <c r="P7" t="n">
-        <v>315.0321333747087</v>
+        <v>315.0927649777191</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -18561,28 +18671,28 @@
         <v>0.0945</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06568720372633052</v>
+        <v>0.06009651449605365</v>
       </c>
       <c r="J8" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K8" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01196109723686845</v>
+        <v>0.01010537801222056</v>
       </c>
       <c r="M8" t="n">
-        <v>3.401933485613759</v>
+        <v>3.410534375049066</v>
       </c>
       <c r="N8" t="n">
-        <v>19.15607586871769</v>
+        <v>19.15989998763453</v>
       </c>
       <c r="O8" t="n">
-        <v>4.376765457357486</v>
+        <v>4.377202301428908</v>
       </c>
       <c r="P8" t="n">
-        <v>317.6591670514667</v>
+        <v>317.7205824314393</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -18639,28 +18749,28 @@
         <v>0.0588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1651079317833358</v>
+        <v>0.1608464162683056</v>
       </c>
       <c r="J9" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K9" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05890218827698046</v>
+        <v>0.05663352276954581</v>
       </c>
       <c r="M9" t="n">
-        <v>3.511496128558194</v>
+        <v>3.506325207360951</v>
       </c>
       <c r="N9" t="n">
-        <v>23.40890957982873</v>
+        <v>23.33930443224686</v>
       </c>
       <c r="O9" t="n">
-        <v>4.838275475810439</v>
+        <v>4.831076943316765</v>
       </c>
       <c r="P9" t="n">
-        <v>323.0490334496275</v>
+        <v>323.0958442473571</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -18717,28 +18827,28 @@
         <v>0.0578</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04986387778425048</v>
+        <v>0.0416701941810287</v>
       </c>
       <c r="J10" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K10" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00554823575061314</v>
+        <v>0.003892459126046299</v>
       </c>
       <c r="M10" t="n">
-        <v>3.402577424421729</v>
+        <v>3.413197204464617</v>
       </c>
       <c r="N10" t="n">
-        <v>23.95206108486239</v>
+        <v>24.06531128879328</v>
       </c>
       <c r="O10" t="n">
-        <v>4.894084294825988</v>
+        <v>4.905640762305499</v>
       </c>
       <c r="P10" t="n">
-        <v>337.5069883815087</v>
+        <v>337.5970000242633</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -18795,28 +18905,28 @@
         <v>0.0639</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01196935367216915</v>
+        <v>0.0117366927459862</v>
       </c>
       <c r="J11" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K11" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004715372010777319</v>
+        <v>0.0004596939541865463</v>
       </c>
       <c r="M11" t="n">
-        <v>2.962296079686862</v>
+        <v>2.948002088011791</v>
       </c>
       <c r="N11" t="n">
-        <v>16.36073332254018</v>
+        <v>16.26035755661487</v>
       </c>
       <c r="O11" t="n">
-        <v>4.044840333380315</v>
+        <v>4.032413366287597</v>
       </c>
       <c r="P11" t="n">
-        <v>340.0070816932176</v>
+        <v>340.0096291797179</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -18873,28 +18983,28 @@
         <v>0.0709</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07610007751315462</v>
+        <v>0.07326269111779173</v>
       </c>
       <c r="J12" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K12" t="n">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0122245357714692</v>
+        <v>0.01148068622263743</v>
       </c>
       <c r="M12" t="n">
-        <v>3.926258177364057</v>
+        <v>3.913833956603141</v>
       </c>
       <c r="N12" t="n">
-        <v>25.15000249402123</v>
+        <v>25.02887413737581</v>
       </c>
       <c r="O12" t="n">
-        <v>5.014977815905193</v>
+        <v>5.002886580502881</v>
       </c>
       <c r="P12" t="n">
-        <v>329.5532702097954</v>
+        <v>329.5844359384</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -18932,7 +19042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M316"/>
+  <dimension ref="A1:M318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40103,6 +40213,140 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>-35.559757213608364,174.48614233610405</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>-35.560115245098245,174.48693118818915</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>-35.56044244980348,174.48773619801304</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-35.5607304581074,174.4885617518676</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-35.56097808826419,174.4894109220844</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-35.561194880928774,174.49030571468194</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-35.56140600960758,174.49119502087598</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-35.56154981258577,174.4920800882417</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-35.5617045926916,174.49300312111356</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-35.56168639143088,174.4939456429433</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-35.561801458551635,174.49484858334958</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>-35.55973865180995,174.48615206529902</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>-35.56010024647334,174.48693904966433</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>-35.56043631775683,174.48773941206935</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-35.56072200580931,174.4885661820107</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-35.56097286010102,174.48941363645784</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-35.56118758998826,174.49030893958897</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-35.5613918679812,174.4912002957797</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-35.56153023847536,174.49208738934794</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-35.56168764541164,174.49300684183038</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-35.56167404872286,174.49394616063935</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-35.5617831599364,174.49484881126213</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
